--- a/mock数据/JD2项目_test-boq/早期介入/交付预案/输出结果/测试用例.xlsx
+++ b/mock数据/JD2项目_test-boq/早期介入/交付预案/输出结果/测试用例.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N53"/>
+  <dimension ref="A1:N54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -496,7 +496,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -516,7 +516,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>机柜硬件检测</t>
+          <t>检查机柜硬件信息。</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -536,15 +536,15 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>将机柜外包装打开。
-记录机柜的产品名称。
-打开柜门后记录电源、计算节点、交换机的数量和型号。</t>
+          <t>将机柜外包装打开
+记录机柜的产品名称
+打开柜门后记录电源、计算节点、交换机的数量和型号</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>根据实际到货情况进行记录。
-根据产品规格记录支持的最大硬件规格。</t>
+          <t>根据实际到货情况进行记录
+根据产品规格记录支持的最大硬件规格</t>
         </is>
       </c>
       <c r="L2" t="inlineStr"/>
@@ -565,7 +565,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>计算节点硬件检测</t>
+          <t>检查计算节点硬件信息。</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -605,15 +605,15 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>将计算节点外包装打开。
-记录计算节点的产品名称。
-打开柜门后记录计算节点的部件信息。</t>
+          <t>将计算节点外包装打开
+记录计算节点的产品名称
+打开柜门后记录计算节点的部件信息</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>根据实际到货情况进行记录。
-根据产品规格记录支持的最大硬件规格。</t>
+          <t>根据实际到货情况进行记录
+根据产品规格记录支持的最大硬件规格</t>
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
@@ -634,7 +634,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -654,7 +654,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>计算节点硬件模块标示测试</t>
+          <t>检查计算节点硬件模块标示是否清晰易辨认。</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -674,8 +674,8 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>检查计算节点外部模块标示是否清晰易辨认，前后面板上各端口、按钮、指示灯标示、产品名称、型号铭牌等，前后面板标识请参考前后面板标识。
-打开机箱盖检查各模块布局是否合理，清晰不遮挡主要部件，不影响通风，内存、风扇、CPU、NPU、PCIe插卡槽位标示清晰。</t>
+          <t>检查计算节点外部模块标示是否清晰易辨认，前后面板上各端口、按钮、指示灯标示、产品名称、型号铭牌等，前后面板标识请参考前后面板标识
+打开机箱盖检查各模块布局是否合理，清晰不遮挡主要部件，不影响通风，内存、风扇、CPU、NPU、PCIe插卡槽位标示清晰</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -697,7 +697,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -717,7 +717,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>计算节点上架测试</t>
+          <t>测试计算节点的上架。</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -737,14 +737,14 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>安装滑轨。
-至少四人从服务器两端水平抬起并放置到滑道上，推入机柜。</t>
+          <t>安装滑轨
+至少四人从服务器两端水平抬起并放置到滑道上，推入机柜</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>服务器能够准确放入到标准机柜中。
-机柜配电合理。</t>
+          <t>服务器能够准确放入到标准机柜中
+机柜配电合理</t>
         </is>
       </c>
       <c r="L5" t="inlineStr"/>
@@ -761,7 +761,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -781,7 +781,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>机柜配电检测</t>
+          <t>测试机柜配电合理。</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -809,11 +809,7 @@
           <t>机柜和计算节点均能正常上电，计算节点能正常上电并进入BIOS，在BIOS里查询到的部件与现场检测到的型号和数量一致。</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>机柜配电合理，接线正确。</t>
-        </is>
-      </c>
+      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="n">
         <v>1</v>
@@ -827,7 +823,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -847,7 +843,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>状态指示灯测试</t>
+          <t>检测被测设备具备基本状态指示灯，并能以明显的不同颜色对设备，或相应部件的状态进行区分。</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -867,9 +863,9 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>接入电源，查看设备前面板Power指示灯并记录状态和颜色显示，查看电源模块是否具备指示灯并记录状态颜色。
-按下计算节点开机按钮，观察Power指示灯并记录状态和颜色显示及变化，查看并记录硬盘、风扇等显示指示灯及颜色显示变化。
-各部件的指示灯状态说明请参考前面板指示灯。</t>
+          <t>接入电源，查看设备前面板Power指示灯并记录状态和颜色显示，查看电源模块是否具备指示灯并记录状态颜色
+按下计算节点开机按钮，观察Power指示灯并记录状态和颜色显示及变化，查看并记录硬盘、风扇等显示指示灯及颜色显示变化
+各部件的指示灯状态说明请参考前面板指示灯</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -878,11 +874,7 @@
         </is>
       </c>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>前面板指示灯 前面板指示灯和按钮示意图 前面板指示灯和按钮说明 标识 指示灯和按钮 状态说明 故障诊断数码管 显示---：表示设备正常。 显示故障码：表示设备有部件故障。 故障码的详细信息，请参见《Atlas 900 A3 SuperPoD 超节点 iBMC 用户指南》。 电源按钮/指示灯 电源按钮说明： 上电状态下短按电源按钮，OS正常关机。 上电状态下长按电源按钮6秒钟，可以将设备强制下电。 待上电状态下短按电源按钮，可以进行上电。 电源指示灯说明： 熄灭：设备未上电。 绿色常亮：设备正常上电。 黄色闪烁：电源按钮暂时处于锁定状态，不能进行操作。设备刚上电，管理系统正在启动时，电源按钮会处于锁定状态。 黄色常亮：设备待上电，待机（Standby）状态。 健康状态指示灯 熄灭：设备未上电或处于异常状态。 红色闪烁（1Hz）：系统有严重告警。 红色闪烁（5Hz）：系统有紧急告警。 绿色常亮：设备运转正常。 UID按钮/指示灯 UID按钮： 可通过手动按UID按钮、iBMC命令或者iBMC的WebUI远程管理使灯熄灭、灯亮或闪烁。 短按UID按钮，可以打开/关闭定位灯。 长按UID按钮5秒左右，可以复位管理系统。 指示灯： UID指示灯用于方便地定位待操作的设备。 熄灭：设备未被定位。 蓝色闪烁：设备被重点定位。 蓝色常亮：设备被定位。 - 网口数据传输状态指示灯 黄色（闪烁）：表示有数据正在传输。 熄灭：表示无数据传输。 - 网口连接状态指示灯 绿色（常亮）：表示网络连接正常。 熄灭：表示网络未连接。 - 硬盘指示灯 硬盘指示灯状态说明详细信息请参见表4-2和表4-3。 风扇模块指示灯 熄灭：设备未上电。 绿色（常亮）：表示风扇正常运作。 红色（闪烁）：表示风扇存在告警。 SATA硬盘指示灯说明 硬盘Active指示灯（绿色指示灯） 硬盘Fault指示灯（红色指示灯） 硬盘Locate指示灯（蓝色指示灯） 状态说明 熄灭 熄灭 熄灭 硬盘不在位。 绿色常亮 熄灭 熄灭 硬盘在位。 绿色闪烁（4Hz） 熄灭 熄灭 硬盘处于正常读写状态或重构主盘状态。 绿色常亮 熄灭 蓝色闪烁（1Hz） 硬盘被RAID卡定位。 绿色闪烁（1Hz） 红色闪烁（1Hz） 熄灭 硬盘处于重构从盘状态。 熄灭 红色常亮 熄灭 RAID组中硬盘被拔出。 绿色常亮 红色常亮 熄灭 RAID组中硬盘故障。 NVMe硬盘指示灯说明 硬盘Active指示灯（绿色指示灯） 硬盘Fault指示灯（红色指示灯） 硬盘Locate指示灯（蓝色指示灯） 状态说明 熄灭 熄灭 熄灭 NVMe硬盘不在位。 绿色常亮 熄灭 熄灭 NVMe硬盘在位且无故障。 绿色闪烁（2Hz） 熄灭 熄灭 NVMe硬盘正在进行读写操作。 熄灭 熄灭 蓝色闪烁（2Hz） NVMe硬盘被OS定位或正处于热插过程中。 熄灭 红色闪烁（0.5Hz） 熄灭 NVMe硬盘已完成热拔出流程，允许拔出。 绿色常亮/灭 红色常亮 熄灭 NVMe硬盘故障。</t>
-        </is>
-      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="n">
         <v>1</v>
       </c>
@@ -895,7 +887,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -915,7 +907,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>计算节点上电测试</t>
+          <t>测计算节点上电正常。</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -935,9 +927,9 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>计算节点上电，按“Del”键进入BIOS，选择“Main”界面。
-在BIOS中记录CPU型号，CPU个数，内存容量等信息。同现场检测到的型号和数量保持一致。
-按“F9”恢复默认设置，后按“F10”保存退出。</t>
+          <t>计算节点上电，按“Del”键进入BIOS，选择“Main”界面
+在BIOS中记录CPU型号，CPU个数，内存容量等信息。同现场检测到的型号和数量保持一致
+按“F9”恢复默认设置，后按“F10”保存退出</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -959,7 +951,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +971,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>RAID配置测试</t>
+          <t>测试计算节点能够配置RAID。</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -999,8 +991,8 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>计算节点安装操作系统之前需要根据实际的应用需要配置RAID，如双盘RAID1、多盘RAID5等。
-基于Atlas支持的RAID卡的设置，请参考《华为服务器 RAID控制卡 用户指南(Arm)》。</t>
+          <t>计算节点安装操作系统之前需要根据实际的应用需要配置RAID，如双盘RAID1、多盘RAID5等
+基于Atlas支持的RAID卡的设置，请参考《华为服务器 RAID控制卡 用户指南(Arm)》</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1022,7 +1014,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1042,7 +1034,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>操作系统安装测试</t>
+          <t>测试计算节点安装操作系统。</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1062,8 +1054,8 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>安装linux操作系统，其他操作系统安装可以参考计算产品兼容性查询助手。
-操作系统安装请参考《Atlas 服务器 操作系统 安装指南 (Arm)》。</t>
+          <t>安装linux操作系统，其他操作系统安装可以参考计算产品兼容性查询助手
+操作系统安装请参考《Atlas 服务器 操作系统 安装指南 (Arm)》</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1089,7 +1081,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1109,7 +1101,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>NPU驱动和固件安装测试</t>
+          <t>测试计算节点安装NPU驱动和固件。</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1129,18 +1121,14 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>安装NPU驱动和NPU固件，详细安装步骤请参考《Atlas A3 中心推理和训练硬件 24.0.RC2 NPU驱动和固件安装指南》的“安装驱动”和“安装固件”章节。
-SSH登录计算节点OS，执行npu-smi info查看驱动加载是否成功。
-执行如下命令查看芯片固件版本号是否与目标版本一致。
-/usr/local/Ascend/driver/tools/upgrade-tool --device_index -1 --component -1 --version</t>
+          <t>0.RC2 NPU驱动和固件安装指南》的“安装驱动”和“安装固件”章节。 SSH登录计算节点OS，执行npu-smi info查看驱动加载是否成功。 执行如下命令查看芯片固件版本号是否与目标版本一致。 /usr/local/Ascend/driver/tools/upgrade-tool --device_index -1 --component -1 --version</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>NPU驱动和NPU固件安装成功，且与目标版本一致。
-若系统出现如下关键回显信息，则表示NPU驱动安装成功。
-Driver package install success!
-若系统出现如下关键回显信息，则表示NPU固件安装成功。
+          <t>NPU驱动和NPU固件安装成功，且与目标版本一致
+若系统出现如下关键回显信息，则表示NPU驱动安装成功
+Driver package install success! 若系统出现如下关键回显信息，则表示NPU固件安装成功
 Firmware package install success! Reboot now or after driver installation for the installation/upgrade to take effect</t>
         </is>
       </c>
@@ -1158,7 +1146,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1178,7 +1166,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>单节点物理算力测试</t>
+          <t>测试单节点物理算力性能</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1203,9 +1191,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>单节点内FP16精度的算力不低于如下值：
-单卡算力：&gt;=752TFLOPS
-单Die算力：&gt;=376TFLOPS</t>
+          <t>单节点内FP16精度的算力不低于如下值： 单卡算力：&gt;=752TFLOPS 单Die算力：&gt;=376TFLOPS</t>
         </is>
       </c>
       <c r="L12" t="inlineStr"/>
@@ -1226,7 +1212,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1246,7 +1232,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>灵衢网络管理网口IP查询和设置测试</t>
+          <t>验证灵衢网络管理网口IP的查询和设置功能。</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1266,26 +1252,20 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>连接计算节点灵衢网络管理网口与交换机。
-使用计算机通过SSH登录灵衢网络管理网口。
-执行如下命令进入MEth0/0/0。
-system-view
-interface MEth0/0/0
-执行如下命令，查询网口IP。
-display this
-执行如下命令，设置新的网口IP。
-ip binding vpn-instance _management_vpn_
-ip address x.x.x.x xx.xx.xx.xx
-说明
-_management_vpn_：灵衢网络管理网口对应VPN名，请根据实际情况修改。
-x.x.x.x：要设置的目标灵衢管理网口IP。
-xx.xx.xx.xx：掩码。</t>
+          <t>连接计算节点灵衢网络管理网口与交换机
+使用计算机通过SSH登录灵衢网络管理网口
+执行如下命令进入MEth0/0/0
+system-view interface MEth0/0/0 执行如下命令，查询网口IP
+display this 执行如下命令，设置新的网口IP
+ip binding vpn-instance _management_vpn_ ip address x.x.x.x xx.xx.xx.xx 说明 _management_vpn_：灵衢网络管理网口对应VPN名，请根据实际情况修改
+x.x.x.x：要设置的目标灵衢管理网口IP
+xx.xx.xx.xx：掩码</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>正常查询灵衢网络管理网口IP。
-正常修改灵衢网络管理网口IP。</t>
+          <t>正常查询灵衢网络管理网口IP
+正常修改灵衢网络管理网口IP</t>
         </is>
       </c>
       <c r="L13" t="inlineStr"/>
@@ -1302,7 +1282,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1322,7 +1302,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>计算节点电子标签查询测试</t>
+          <t>测试计算节点电子标签查询功能。</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1342,9 +1322,9 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>连接计算节点灵衢网络管理网口与交换机。
-使用计算机通过SSH登录灵衢网络管理网口。
-执行display device elabel命令查询电子标签。</t>
+          <t>连接计算节点灵衢网络管理网口与交换机
+使用计算机通过SSH登录灵衢网络管理网口
+执行display device elabel命令查询电子标签</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1366,7 +1346,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1386,7 +1366,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>计算节点灵衢总线板与灵衢总线和以太板CPLD版本信息查询测试</t>
+          <t>测试计算节点灵衢总线板与灵衢总线和以太板CPLD版本信息查询。</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1406,16 +1386,16 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>连接计算节点灵衢网络管理网口与交换机。
-使用计算机通过SSH登录灵衢网络管理网口。
-执行display device card命令查询子卡信息。
-执行display version命令查询CPLD版本。</t>
+          <t>连接计算节点灵衢网络管理网口与交换机
+使用计算机通过SSH登录灵衢网络管理网口
+执行display device card命令查询子卡信息
+执行display version命令查询CPLD版本</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>若系统出现如下回显信息，则表示成功查询子卡数量。
-若系统出现如下回显信息，则表示成功查询CPLD版本信息。</t>
+          <t>若系统出现如下回显信息，则表示成功查询子卡数量
+若系统出现如下回显信息，则表示成功查询CPLD版本信息</t>
         </is>
       </c>
       <c r="L15" t="inlineStr"/>
@@ -1432,7 +1412,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1452,7 +1432,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>计算节点光口状态查询测试</t>
+          <t>测试计算节点光口状态查询。</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1472,18 +1452,18 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>连接计算节点灵衢网络管理网口与交换机。
-使用计算机通过SSH登录灵衢网络管理网口。
-执行display interface brief命令查询总体端口状态，其中400GHL端口为灵衢交换机接口。
-执行display interface+灵衢交换机接口查询具体光口信息。
-执行如下命令，在OS内查询参数面接口信息。
+          <t>连接计算节点灵衢网络管理网口与交换机
+使用计算机通过SSH登录灵衢网络管理网口
+执行display interface brief命令查询总体端口状态，其中400GHL端口为灵衢交换机接口
+执行display interface+灵衢交换机接口查询具体光口信息
+执行如下命令，在OS内查询参数面接口信息
 for i in $(seq 0 15); do echo "==============&gt; $i"; hccn_tool -i $i -link -g;done</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>灵衢交换机接口状态查询正常，为对应端口的实际连接状况。
-覆盖参数面接口状态查询正常，为对应端口的实际连接状况。</t>
+          <t>灵衢交换机接口状态查询正常，为对应端口的实际连接状况
+覆盖参数面接口状态查询正常，为对应端口的实际连接状况</t>
         </is>
       </c>
       <c r="L16" t="inlineStr"/>
@@ -1504,7 +1484,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1524,7 +1504,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>计算节点光模块信息查询测试</t>
+          <t>测试计算节点光模块信息查询。</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1544,10 +1524,10 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>连接计算节点灵衢网络管理网口与交换机。
-使用计算机通过SSH登录灵衢网络管理网口。
-执行display interface transceiver命令查询光模块信息，回显如下。
-执行如下命令，在OS内查询参数面接口信息，部分回显如下。
+          <t>连接计算节点灵衢网络管理网口与交换机
+使用计算机通过SSH登录灵衢网络管理网口
+执行display interface transceiver命令查询光模块信息，回显如下
+执行如下命令，在OS内查询参数面接口信息，部分回显如下
 for i in $(seq 0 15); do echo "==============&gt; $i"; hccn_tool -i $i -optical-g;done</t>
         </is>
       </c>
@@ -1570,7 +1550,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1590,7 +1570,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>计算节点温度管理测试</t>
+          <t>测试计算节点温度管理。</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1610,9 +1590,9 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>连接计算节点灵衢网络管理网口与交换机。
-使用计算机通过SSH登录灵衢网络管理网口。
-执行display device temperature命令读取传感器温度，回显如下。</t>
+          <t>连接计算节点灵衢网络管理网口与交换机
+使用计算机通过SSH登录灵衢网络管理网口
+执行display device temperature命令读取传感器温度，回显如下</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1634,7 +1614,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1654,7 +1634,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>计算节点光模块降lane测试</t>
+          <t>测试光模块降lane的能力。</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1674,19 +1654,18 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>连接计算节点灵衢网络管理网口与交换机。
-使用计算机通过SSH登录灵衢网络管理网口。
-执行如下命令查看光模块lane信息，端口状态，告警信息。
-display forward information enp slot 1 chip 0 "get port lane-state port-id 18"
-光模块第2条和第3条lane故障，查看光模块lane信息，端口状态，告警信息。
-光模块lane故障消除，查看光模块lane信息，端口状态，告警信息。</t>
+          <t>连接计算节点灵衢网络管理网口与交换机
+使用计算机通过SSH登录灵衢网络管理网口
+执行如下命令查看光模块lane信息，端口状态，告警信息
+display forward information enp slot 1 chip 0 "get port lane-state port-id 18" 光模块第2条和第3条lane故障，查看光模块lane信息，端口状态，告警信息
+光模块lane故障消除，查看光模块lane信息，端口状态，告警信息</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>光模块满lane建链，端口up，无降lane告警；
-端口上报降lane告警，端口up；
-端口降lane告警撤销，端口up。</t>
+          <t>光模块满lane建链，端口up，无降lane告警
+端口上报降lane告警，端口up
+端口降lane告警撤销，端口up</t>
         </is>
       </c>
       <c r="L19" t="inlineStr"/>
@@ -1703,7 +1682,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1723,7 +1702,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>BGP配置方案及收敛</t>
+          <t>BGP（边界网关协议）配置方案及收敛。</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1731,7 +1710,11 @@
           <t>BGP（边界网关协议）配置方案及收敛。</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr"/>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
       <c r="I20" t="inlineStr">
         <is>
           <t>超节点设备加载Atlas 900 A3 SuperPoD 超节点规划文件，设备初始化完成。</t>
@@ -1739,20 +1722,20 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Atlas 900 A3 SuperPoD 超节点加载对应的规划文件启动，配置交换机位置信息，所有L1在同一个租户群；
-超节点L1、L2分别部署BGP，建立BGP邻居；
-从L1-1与L1-2跨节点互访打流；
-关闭L1-1网络侧端口；
-执行undo shutdown命令后重新打流，L1-1网络侧端口建链成功。</t>
+          <t>Atlas 900 A3 SuperPoD 超节点加载对应的规划文件启动，配置交换机位置信息，所有L1在同一个租户群
+超节点L1、L2分别部署BGP，建立BGP邻居
+从L1-1与L1-2跨节点互访打流
+关闭L1-1网络侧端口
+执行undo shutdown命令后重新打流，L1-1网络侧端口建链成功</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>环境启动正常、租户信息正确；
-查询到所有peer处于establish状态所有设备上都能通过BGP学习到相互之间的路由；
-流量经网络侧端口通过L2的两个芯片转发；
-流量中断，BGP建链中断，通过BGP学习到的对端的路由被删除、无表项残留；
-BGP建链恢复，通过BGP学习到的对端的路由恢复，流量经网络侧端口通过L2的两个芯片转发。</t>
+          <t>环境启动正常、租户信息正确
+查询到所有peer处于establish状态所有设备上都能通过BGP学习到相互之间的路由
+流量经网络侧端口通过L2的两个芯片转发
+流量中断，BGP建链中断，通过BGP学习到的对端的路由被删除、无表项残留
+BGP建链恢复，通过BGP学习到的对端的路由恢复，流量经网络侧端口通过L2的两个芯片转发</t>
         </is>
       </c>
       <c r="L20" t="inlineStr"/>
@@ -1789,7 +1772,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>机柜RM211的管理iBMC IP查询和设置测试</t>
+          <t>查询，设置RM211管理模块的iBMC的IP地址。</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1809,8 +1792,8 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>机柜上电，根据默认账号密码登录RM211 Web界面。
-在web页面上方点击“IRM管理”，左侧栏目点击“网络配置”，在右侧“网络协议”项中对IP进行修改。</t>
+          <t>机柜上电，根据默认账号密码登录RM211 Web界面
+在web页面上方点击“IRM管理”，左侧栏目点击“网络配置”，在右侧“网络协议”项中对IP进行修改</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1819,7 +1802,11 @@
         </is>
       </c>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>默认iBMC IP地址：192.168.2.100</t>
+        </is>
+      </c>
       <c r="N21" t="n">
         <v>1</v>
       </c>
@@ -1852,7 +1839,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>计算节点iBMC IP查询和设置测试</t>
+          <t>查询，设置计算节点iBMC的IP地址。</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1872,11 +1859,11 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>计算节点上电，按“Del”键进入BIOS，选择“Advanced”界面。
-选择“IPMI iBMC Configuration”，按“Enter”进入“IPMI iBMC Configuration”配置界面。
-选择“iBMC Configuration”，按“Enter”进入“iBMC Configuration”配置页面。
-选择“IPv4 configuration下的IP Address”，按“Enter”进入IP地址设置界面，可以查询、修改iBMC网口的IP地址。
-设置IP后保存退出，不需要重启iBMC。</t>
+          <t>计算节点上电，按“Del”键进入BIOS，选择“Advanced”界面
+选择“IPMI iBMC Configuration”，按“Enter”进入“IPMI iBMC Configuration”配置界面
+选择“iBMC Configuration”，按“Enter”进入“iBMC Configuration”配置页面
+选择“IPv4 configuration下的IP Address”，按“Enter”进入IP地址设置界面，可以查询、修改iBMC网口的IP地址
+设置IP后保存退出，不需要重启iBMC</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1885,7 +1872,11 @@
         </is>
       </c>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>默认iBMC IP地址：192.168.2.100</t>
+        </is>
+      </c>
       <c r="N22" t="n">
         <v>1</v>
       </c>
@@ -1918,7 +1909,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>计算节点远程上电和下电测试</t>
+          <t>测试计算节点能够通过远程控制上电，下电。</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1938,8 +1929,8 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>进入计算节点iBMC的web页面。
-在web页面上方点击“系统管理”，左侧栏目点击“电源&amp;功率”，选择“服务器上下电”，点击右边窗口中的电源虚拟按键完成上下电控制。</t>
+          <t>进入计算节点iBMC的web页面
+在web页面上方点击“系统管理”，左侧栏目点击“电源&amp;功率”，选择“服务器上下电”，点击右边窗口中的电源虚拟按键完成上下电控制</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1981,7 +1972,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>计算节点部件信息查询测试</t>
+          <t>测试可以通过iBMC管理页面获取计算节点主要部件信息。</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -2001,17 +1992,17 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>进入计算节点iBMC的web页面。
-在web页面上方点击“系统管理”，左侧栏目点击“系统信息”，在右边的窗口可以看到各个部件信息。
-CPU（厂商、型号、主频、核数、缓存等）部件信息。
-NPU（厂商、型号、功率、固件版本、DIE ID等）部件信息。
-内存（厂商、容量、速度、类型、电压、位宽等）部件信息。
-网络适配器（型号、厂商、资源归属、总线信息等）部件信息。
-传感器（状态、门限等）部件信息。
-在web页面上方点击“系统管理”，左侧栏目点击“电源&amp;功率”，在右边的窗口可以看到电源信息。
-电源（厂商、额定功率、输入模式、电压等）部件信息。
-在web页面上方点击“系统管理”，左侧栏目点击“风扇&amp;散热”，在右边的窗口可以看到风扇信息。
-风扇（型号、转速、速率比、部件编码）部件信息。</t>
+          <t>进入计算节点iBMC的web页面
+在web页面上方点击“系统管理”，左侧栏目点击“系统信息”，在右边的窗口可以看到各个部件信息
+CPU（厂商、型号、主频、核数、缓存等）部件信息
+NPU（厂商、型号、功率、固件版本、DIE ID等）部件信息
+内存（厂商、容量、速度、类型、电压、位宽等）部件信息
+网络适配器（型号、厂商、资源归属、总线信息等）部件信息
+传感器（状态、门限等）部件信息
+在web页面上方点击“系统管理”，左侧栏目点击“电源&amp;功率”，在右边的窗口可以看到电源信息
+电源（厂商、额定功率、输入模式、电压等）部件信息
+在web页面上方点击“系统管理”，左侧栏目点击“风扇&amp;散热”，在右边的窗口可以看到风扇信息
+风扇（型号、转速、速率比、部件编码）部件信息</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -2053,7 +2044,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>计算节点L1交换网络端口查询测试</t>
+          <t>测试通过管理页面获取计算节点L1交换网络端口信息。</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -2073,9 +2064,9 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>连接计算节点灵衢网络管理网口与交换机。
-使用计算机通过SSH登录灵衢网络管理网口。
-执行display interface brief | include up命令查询L1交换网络端口状态信息。</t>
+          <t>连接计算节点灵衢网络管理网口与交换机
+使用计算机通过SSH登录灵衢网络管理网口
+执行display interface brief | include up命令查询L1交换网络端口状态信息</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -2117,7 +2108,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>设备一键式收集日志的功能测试</t>
+          <t>测试设备一键式收集日志的功能。</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -2137,16 +2128,16 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>连接计算节点灵衢网络管理网口与交换机。
-使用计算机通过SSH登录灵衢网络管理网口。
-交换芯片上诊断视图执行collect diagnostic information。
-用户视图查询文件dir *.zip。</t>
+          <t>连接计算节点灵衢网络管理网口与交换机
+使用计算机通过SSH登录灵衢网络管理网口
+交换芯片上诊断视图执行collect diagnostic information
+用户视图查询文件dir *.zip</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>命令下发成功；
-成功生成日志文件：diagnostic_information.zip。</t>
+          <t>命令下发成功
+成功生成日志文件：diagnostic_information.zip</t>
         </is>
       </c>
       <c r="L26" t="inlineStr"/>
@@ -2183,7 +2174,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>设备HCCS场景下ZTP装机功能测试</t>
+          <t>测试设备HCCS场景下ZTP（零配置部署）装机功能。</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -2203,14 +2194,14 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>设备使能ZTP功能，设备空配置上电或空配置重启；
-设备启动后执行display startup命令查询设备信息。</t>
+          <t>设备使能ZTP功能，设备空配置上电或空配置重启
+设备启动后执行display startup命令查询设备信息</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>设备上电/重启成功；
-设备正常启动后，能够查到设备启动信息，启动大包配置文件补丁等启动信息与ztp.ini中间文件一致。</t>
+          <t>设备上电/重启成功
+设备正常启动后，能够查到设备启动信息，启动大包配置文件补丁等启动信息与ztp.ini中间文件一致</t>
         </is>
       </c>
       <c r="L27" t="inlineStr"/>
@@ -2247,7 +2238,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>计算节点健康检查测试</t>
+          <t>检查计算节点的健康状态，涵盖RoCE网卡link状态、通用网卡光链路收发功率、NPU光信号误码率、TLS开关状态一致性、网络健康状态、光模块接收功率、hccp残留进程、RoCE网卡网络错包、节点防火墙及NPU设备健康诊断等多个维度，确保计算节点整体健康。</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -2267,12 +2258,12 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>从CloudOps Toolkit左侧菜单进入“硬件初始化 &gt; 健康检查”页面。
-单击“创建任务”，设置任务信息，单击“确定”。
-单击任务名称，进入“选择节点”环节，导入节点信息进行连通性检测。
-在“选择检查项目”环节，根据测试需求选择场景，若选择自定义，则可在下方勾选需要的测试项，测试项包括“健康状态、配置信息、版本兼容性信息、资产信息、安全配置信息、IBMS信息收集及证书信息”等，配置并发数，完成后单击“下一步”。
-弹出窗口点击“确认”，开始健康检查。
-在“健康检查”页面等待检查完成，并查看健康报告。</t>
+          <t>从CloudOps Toolkit左侧菜单进入“硬件初始化 &gt; 健康检查”页面
+单击“创建任务”，设置任务信息，单击“确定”
+单击任务名称，进入“选择节点”环节，导入节点信息进行连通性检测
+在“选择检查项目”环节，根据测试需求选择场景，若选择自定义，则可在下方勾选需要的测试项，测试项包括“健康状态、配置信息、版本兼容性信息、资产信息、安全配置信息、IBMS信息收集及证书信息”等，配置并发数，完成后单击“下一步”
+弹出窗口点击“确认”，开始健康检查
+在“健康检查”页面等待检查完成，并查看健康报告</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2314,7 +2305,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>供电冗余测试</t>
+          <t>测试电源是否冗余。</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -2334,9 +2325,9 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>安装好8个电源线缆。
-计算节点上电并进入操作系统。
-拔出其中1个电源线。</t>
+          <t>安装好8个电源线缆
+计算节点上电并进入操作系统
+拔出其中1个电源线</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2378,7 +2369,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>电源冗余测试</t>
+          <t>测试电源框电源是否冗余。</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2398,9 +2389,9 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>安装好24个电源模块。
-计算节点上电并进入操作系统。
-拔出其中1个电源模块。</t>
+          <t>安装好24个电源模块
+计算节点上电并进入操作系统
+拔出其中1个电源模块</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2442,7 +2433,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>风扇冗余测试</t>
+          <t>测试计算节点风扇是否冗余。</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2462,10 +2453,10 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>计算节点上电，进入操作系统。
-进入iBMC管理页面，获取风扇当前转速。
-拔掉计算节点任意一个风扇电源，测试是否能够进入操作系统。
-进入iBMC管理页面，获取风扇当前转速。</t>
+          <t>计算节点上电，进入操作系统
+进入iBMC管理页面，获取风扇当前转速
+拔掉计算节点任意一个风扇电源，测试是否能够进入操作系统
+进入iBMC管理页面，获取风扇当前转速</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2507,7 +2498,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>硬盘冗余测试</t>
+          <t>测试计算节点可以实现硬盘冗余。</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2527,16 +2518,16 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>计算节点上电，给计算节点配置2盘RAID1。
-安装操作系统。
-拔出RAID1中其中一块硬盘，测试操作系统是否可以继续正常运行。
-插入一块同型号的全新硬盘，测试RAID1是否自动恢复。</t>
+          <t>计算节点上电，给计算节点配置2盘RAID1
+安装操作系统
+拔出RAID1中其中一块硬盘，测试操作系统是否可以继续正常运行
+插入一块同型号的全新硬盘，测试RAID1是否自动恢复</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>拔掉其中一块硬盘后，操作系统可以继续正常运行。
-插入同型号的全新硬盘后RAID1自动恢复。</t>
+          <t>拔掉其中一块硬盘后，操作系统可以继续正常运行
+插入同型号的全新硬盘后RAID1自动恢复</t>
         </is>
       </c>
       <c r="L32" t="inlineStr"/>
@@ -2577,7 +2568,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>模块拔插告警上报测试</t>
+          <t>测试模块拔插告警上报。</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2585,7 +2576,11 @@
           <t>测试模块拔插告警上报。</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr"/>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
       <c r="I33" t="inlineStr">
         <is>
           <t>计算节点正常上电。</t>
@@ -2593,16 +2588,16 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>查看互联端口信息，查询告警信息；
-拔除光模块，查询端口信息，查询告警信息；
-再重新插入光模块，查询端口信息，查询告警信息。</t>
+          <t>查看互联端口信息，查询告警信息
+拔除光模块，查询端口信息，查询告警信息
+再重新插入光模块，查询端口信息，查询告警信息</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>端口up；
-光模块拔除成功，端口down，上报光模块拔除告警；
-光模块插入成功，端口up，光模块拔除告警消除。</t>
+          <t>端口up
+光模块拔除成功，端口down，上报光模块拔除告警
+光模块插入成功，端口up，光模块拔除告警消除</t>
         </is>
       </c>
       <c r="L33" t="inlineStr"/>
@@ -2639,7 +2634,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>计算节点光模块信号震荡压力测试</t>
+          <t>光模块信号震荡压力测试。</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2647,7 +2642,11 @@
           <t>光模块信号震荡压力测试。</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr"/>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
       <c r="I34" t="inlineStr">
         <is>
           <t>设备正常上电，互连状态。</t>
@@ -2655,16 +2654,16 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>DUT1和DUT2查看互连端口状态；
-DUT1光模块信号震荡压力测试，反复执行shutdown undo shutdown；
-DUT1确保最后一次undo shutdown，查询端口状态。</t>
+          <t>DUT1和DUT2查看互连端口状态
+DUT1光模块信号震荡压力测试，反复执行shutdown undo shutdown
+DUT1确保最后一次undo shutdown，查询端口状态</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>DUT1和DUT2光模块互连端口up；
-命令下发成功；
-命令下发成功，端口up。</t>
+          <t>DUT1和DUT2光模块互连端口up
+命令下发成功
+命令下发成功，端口up</t>
         </is>
       </c>
       <c r="L34" t="inlineStr"/>
@@ -2701,7 +2700,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>长时间稳定性压力测试</t>
+          <t>Stress长时间稳定性压力测试。</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2721,14 +2720,12 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>添加环境变量。
-以root用户登录计算节点，执行vi ~/.bashrc命令，参见《MindX ToolBox 用户指南》配置环境变量。
-运行CPU加压软件，以stress为例。
-stress --cpu {CPU核数}
-注：cpu核数可以用下列命令进行查询。
-# cat /proc/cpuinfo| grep "processor"| wc -l
-压测结束后停止CPU的加压进程。
-新打开一个界面窗口，执行如下命令，给NPU加压。
+          <t>添加环境变量
+以root用户登录计算节点，执行vi ~/.bashrc命令，参见《MindX ToolBox 用户指南》配置环境变量
+运行CPU加压软件，以stress为例
+stress --cpu {CPU核数} 注：cpu核数可以用下列命令进行查询
+# cat /proc/cpuinfo| grep "processor"| wc -l 压测结束后停止CPU的加压进程
+新打开一个界面窗口，执行如下命令，给NPU加压
 ascend-dmi -p -dur 43200 -it 5 -pm refresh</t>
         </is>
       </c>
@@ -2775,7 +2772,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>单机综合测试-含参数面</t>
+          <t>基于Atlas 900 A3 SuperPoD服务器，进行软件版本检查、NPU芯片健康检查、节点内HCCS带宽性能测试、灵衢总线检查等测试项，并测试参数面RoCE网络</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2795,20 +2792,17 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>从CloudOps Toolkit左侧菜单进入“单机测试 &gt; 单机综合检测”页面。
-单击“创建任务”，设置任务信息，单击“确定”。
-单击任务名称，进入“选择节点”环节，导入节点信息进行连通性检测。
-在“信息采集”环节，单击“当前模板”选择已有模板，名称“全量检测-A3服务器（风冷，液冷）”检查项按照模板中默认勾选，单击“全量采集”。
-配置参数，开启单机综合测试定时任务。
-在“健康分析”页面，点击“执行检查。</t>
+          <t>从CloudOps Toolkit左侧菜单进入“单机测试 &gt; 单机综合检测”页面
+单击“创建任务”，设置任务信息，单击“确定”
+单击任务名称，进入“选择节点”环节，导入节点信息进行连通性检测
+在“信息采集”环节，单击“当前模板”选择已有模板，名称“全量检测-A3服务器（风冷，液冷）”检查项按照模板中默认勾选，单击“全量采集”
+配置参数，开启单机综合测试定时任务
+在“健康分析”页面，点击“执行检查</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>进入页面成功，无报错
-成功创建任务，无报错
-成功导入节点，完成连通性检测
-成功采集信息，并得到健康分析报告，测试结果无Fail项</t>
+          <t>进入页面成功，无报错  成功创建任务，无报错  成功导入节点，完成连通性检测  成功采集信息，并得到健康分析报告，测试结果无Fail项</t>
         </is>
       </c>
       <c r="L36" t="inlineStr"/>
@@ -2845,7 +2839,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>单机综合测试-不含参数面</t>
+          <t>基于Atlas 900 A3 SuperPoD服务器，进行软件版本检查、NPU芯片健康检查、节点内HCCS带宽性能测试、灵衢总线检查等测试项</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2865,20 +2859,17 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>从CloudOps Toolkit左侧菜单进入“单机测试 &gt; 单机综合检测”页面。
-单击“创建任务”，设置任务信息，单击“确定”。
-单击任务名称，进入“选择节点”环节，导入节点信息进行连通性检测。
-在“信息采集”环节，单击“当前模板”选择已有模板，名称“无参数面-A3服务器”检查项按照模板中默认勾选，单击“全量采集”。
-配置参数，开启单机综合测试定时任务。
-在“健康分析”页面，点击“执行检查。</t>
+          <t>从CloudOps Toolkit左侧菜单进入“单机测试 &gt; 单机综合检测”页面
+单击“创建任务”，设置任务信息，单击“确定”
+单击任务名称，进入“选择节点”环节，导入节点信息进行连通性检测
+在“信息采集”环节，单击“当前模板”选择已有模板，名称“无参数面-A3服务器”检查项按照模板中默认勾选，单击“全量采集”
+配置参数，开启单机综合测试定时任务
+在“健康分析”页面，点击“执行检查</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>进入页面成功，无报错
-成功创建任务，无报错
-成功导入节点，完成连通性检测
-成功采集信息，并得到健康分析报告，测试结果无Fail项</t>
+          <t>进入页面成功，无报错  成功创建任务，无报错  成功导入节点，完成连通性检测  成功采集信息，并得到健康分析报告，测试结果无Fail项</t>
         </is>
       </c>
       <c r="L37" t="inlineStr"/>
@@ -2915,7 +2906,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>单机模型训练测试-Qwen3-32B</t>
+          <t>对基于PyTorch框架的qwen3-32b模型进行训练，测试训练性能</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2935,14 +2926,9 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>在CloudOps工具首页选择“AI训练 &gt; 服务器  &gt; 单机测试”，进入“单机测试”页面。
-单击“单机测试”
-单击“单机模型训练”，进入单机训练测试界面。
-参数配置（参考算力军团发布的模型测试基线）
-单击“下一步”，进入“环境检查”界面
-上传模型镜像文件。若待训练的节点服务器已包含模型镜像文件，可直接单击“下一步”，跳过本步骤
-进入“测试执行”界面，启动测试
-集群训练过程中，可单击“查询最新状态”查看训练状态。服务器启动训练任务后，可单击“查询日志”，单击“刷新”，查看工具运行日志和训练日志。
+          <t>在CloudOps工具首页选择“AI训练 &gt; 服务器  &gt; 单机测试”，进入“单机测试”页面
+单击“单机测试” 单击“单机模型训练”，进入单机训练测试界面
+参数配置（参考算力军团发布的模型测试基线） 单击“下一步”，进入“环境检查”界面 上传模型镜像文件。若待训练的节点服务器已包含模型镜像文件，可直接单击“下一步”，跳过本步骤 进入“测试执行”界面，启动测试 集群训练过程中，可单击“查询最新状态”查看训练状态。服务器启动训练任务后，可单击“查询日志”，单击“刷新”，查看工具运行日志和训练日志
 测试完成后（“当前状态”显示训练任务已完成），可单击“生成报告”，将测试报告保存至本地</t>
         </is>
       </c>
@@ -2985,17 +2971,17 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>灵衢PRBS测试（L1/L2双向压测）</t>
+          <t>NPU RoCE平面、超节点平面的点对点流量转发测试，测试其互通性。</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>针对Atlas A3 Supper Pod 灵衢总线链路光模块进行PRBS压测； 压测涉及的范围：计算节点灵衢总线板(L1)和灵衢总线设备(L2)之间链路； 如果有客户要求提供流量转发测试报告，可以使用CloudopsToolKit/Computing ToolKit工具进行NPU RoCE平面、超节点平面的点对点流量转发测试；如果客户无需求，则无需进行此项检测。 测试内容 对节点间通过ROCE参数面或HCCS平面进行数据转发流量大小进行测试。 使用ROCE协议，节点内支持的打流方式：NPU-NPU 使用ROCE协议，跨节点支持的打流方式：NPU-NPU 使用HCCS协议，节点内支持的打流方式如下： CPU-NPU NPU-CPU NPU-NPU 使用HCCS协议，跨节点支持的打流方式：NPU-NPU 测试依赖 进行打流测试前，已完成设备纳管和光链路连通性检查。 已准备好超节点LLD规划文件； 测试项 测试类型 测试说明 打流类型 RoCE参数面打流：选择RoCE参数面打流类型，需要设置执行测试运行时间。 取值范围1~500s ，默认值：5。 HCCS平面打流：选择HCCS平面打流类型，需要设置拷贝次数和传输数据 大小。 – 拷贝次数：取值范围：1-100000000。默认值：40。 – 传输数据大小（MB）：取值范围：1-4096。默认值： 1024 打流方式 全量打流：对全部设备进行流量转发。 自定义打流：可选择对应设备进行流量转发。如果打流类 型为“超节点平面打流”，则不能跨超节点进行流量转发，如果打流类型为“RoCE参数面打流”则可以跨超节点进行流量转发。 操作指导 用例名称 灵衢总线参数面打流测试 NPU RoCE平面、超节点平面的点对点流量转发测试，测试其互通性。</t>
+          <t>NPU RoCE平面、超节点平面的点对点流量转发测试，测试其互通性。</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>384超节点 384超节点组网</t>
+          <t>384超节点组网</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -3005,44 +2991,22 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>1）L1-&gt;L2压力测试：
-step1、使能L1光模块端口的TX PRBS；
-step 2、使能L2光模块端口的RX PRBS；
-step 3、等待6h后，在L2总线设备获取PRBS压测结果， 并关闭L2光模块端口的RX PRBS；
-step 4、关闭L1光模块端口的TX PRBS。
-2）L2-&gt;L1压力测试
-step1、使能L2光模块端口的TX PRBS；
-step 2、使能L1光模块端口的RX PRBS；
-step 3、等待10h后，在L1设备获取PRBS压测结果， 并关闭L1光模块端口的RX PRBS；
-step 4、关闭L2光模块端口的TX PRBS。
-对节点间通过ROCE参数面或HCCS平面进行数据转发流量大小进行测试。
-使用ROCE协议，节点内支持的打流方式：NPU-NPU
-使用ROCE协议，跨节点支持的打流方式：NPU-NPU
-使用HCCS协议，节点内支持的打流方式如下：
-CPU-NPU
-NPU-CPU
-NPU-NPU
-使用HCCS协议，跨节点支持的打流方式：NPU-NPU
-打流类型		RoCE参数面打流：选择RoCE参数面打流类型，需要设置执行测试运行时间。 取值范围1~500s ，默认值：5。
-	HCCS平面打流：选择HCCS平面打流类型，需要设置拷贝次数和传输数据 大小。
-– 拷贝次数：取值范围：1-100000000。默认值：40。
-– 传输数据大小（MB）：取值范围：1-4096。默认值： 1024
-打流方式		全量打流：对全部设备进行流量转发。
-	自定义打流：可选择对应设备进行流量转发。如果打流类 型为“超节点平面打流”，则不能跨超节点进行流量转发，如果打流类型为“RoCE参数面打流”则可以跨超节点进行流量转发。</t>
+          <t>对节点间通过ROCE参数面或HCCS平面进行数据转发流量大小进行测试
+使用ROCE协议，节点内支持的打流方式：NPU-NPU 使用ROCE协议，跨节点支持的打流方式：NPU-NPU 使用HCCS协议，节点内支持的打流方式如下： CPU-NPU NPU-CPU NPU-NPU 使用HCCS协议，跨节点支持的打流方式：NPU-NPU  打流类型		RoCE参数面打流：选择RoCE参数面打流类型，需要设置执行测试运行时间
+取值范围1~500s ，默认值：5
+	HCCS平面打流：选择HCCS平面打流类型，需要设置拷贝次数和传输数据 大小
+– 拷贝次数：取值范围：1-100000000。默认值：40
+– 传输数据大小（MB）：取值范围：1-4096。默认值： 1024 打流方式		全量打流：对全部设备进行流量转发
+	自定义打流：可选择对应设备进行流量转发。如果打流类 型为“超节点平面打流”，则不能跨超节点进行流量转发，如果打流类型为“RoCE参数面打流”则可以跨超节点进行流量转发</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>导出压测报告“index.html”文件，查看设备的业务流是否都执行成功。
-选择设备，单击PRBS结果查询指令“详情”，进入详情页，查看PRBS压测结果是否符合预期（如下图：RX侧查询到光模块PRBS为1e-24，即 10-24，小于10-6）
-如发现误码率结果不符合预期，则需定位分析。</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>流量转发测试任务执行完成后，单击“导出报告”，导出执行结果。 如果打流类型为“RoCE参数面打流”，导出报告需要设置带宽阈值和保存路径。 – 带宽阈值（MB/s）：取值范围 1-100000，默认值为20000。 – 保存路径：单击“选择目录”，选择报告保存的本地路径。 如果打流类型为“超节点平面打流”，导出报告时需要设置单向带宽阈值、双向 带宽阈值、保存路径。 – 双向带宽阈值（GB/s）：取值范围 1-1000，默认值为200。 – 单向带宽阈值（GB/s）：取值范围 0-1000，默认值为100。 – 保存路径：单击“选择目录”，选择报告保存的本地路径。</t>
-        </is>
-      </c>
+          <t>导出压测报告“index.html”文件，查看设备的业务流是否都执行成功
+选择设备，单击PRBS结果查询指令“详情”，进入详情页，查看PRBS压测结果是否符合预期（如下图：RX侧查询到光模块PRBS为1e-24，即 10-24，小于10-6）  如发现误码率结果不符合预期，则需定位分析</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr"/>
       <c r="N39" t="n">
         <v>1</v>
@@ -3076,7 +3040,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>集群健康检查测试</t>
+          <t>检查超节点的健康状态，涵盖RoCE网卡link状态、通用网卡光链路收发功率、NPU光信号误码率、TLS开关状态一致性、网络健康状态、光模块接收功率、hccp残留进程、RoCE网卡网络错包、节点防火墙及NPU设备健康诊断等多个维度，确保计算节点整体健康。</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -3096,12 +3060,12 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>从CloudOps Toolkit左侧菜单进入“硬件初始化 &gt; 健康检查”页面。
-单击“创建任务”，设置任务信息，单击“确定”。
-单击任务名称，进入“选择节点”环节，导入节点信息进行连通性检测。
-在“选择检查项目”环节，根据测试需求选择场景，若选择自定义，则可在下方勾选需要的测试项，测试项包括“健康状态、配置信息、版本兼容性信息、资产信息、安全配置信息、IBMS信息收集及证书信息”等，配置并发数，完成后单击“下一步”。
-弹出窗口点击“确认”，开始健康检查。
-在“健康检查”页面等待检查完成，并查看健康报告。</t>
+          <t>从CloudOps Toolkit左侧菜单进入“硬件初始化 &gt; 健康检查”页面
+单击“创建任务”，设置任务信息，单击“确定”
+单击任务名称，进入“选择节点”环节，导入节点信息进行连通性检测
+在“选择检查项目”环节，根据测试需求选择场景，若选择自定义，则可在下方勾选需要的测试项，测试项包括“健康状态、配置信息、版本兼容性信息、资产信息、安全配置信息、IBMS信息收集及证书信息”等，配置并发数，完成后单击“下一步”
+弹出窗口点击“确认”，开始健康检查
+在“健康检查”页面等待检查完成，并查看健康报告</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -3143,7 +3107,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>集合通信性能测试-单Pod-16节点</t>
+          <t>基于Atlas 900 A3 SuperPoD服务器，使用CloudOps验收集群功能测试，进行参数面集合通信性能测试功能验收</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -3163,15 +3127,13 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>从工具CloudOps ToolKit首页菜单进入“AI训练 &gt; 服务器”页面。
-在AI训练-服务器界面右侧进入 “集群测试 &gt; 集合通信测试”，设置任务信息，单击“确定”。
-单机“创建”，输入“任务名称”及“任务描述”
-单击任务名称，进入“任务配置”界面，导入节点信息进行连通性检测，完成后单击“下一步”
-进入“分组配置”界面，单击“分组配置”在“自动分组”下输入“分组切片大小”为16，完成后单击“下一步”。
-进入"参数配置"界面，在“测试参数配置”处设置相关参数，（测试数据起始大小1G，结束大小16G，遍历测试所有集合通信算子），完成后单击“下一步”。
-进入“环境准备”界面，每次执行建议先进行“环境恢复”，再进行“环境检查”，完成后单击“下一步”。
-进入“通信测试”界面，单击“执行”开始通信测试任务。
-测试任务执行完成后，单击“导出测试报告”，保存测试结果。</t>
+          <t>从工具CloudOps ToolKit首页菜单进入“AI训练 &gt; 服务器”页面
+在AI训练-服务器界面右侧进入 “集群测试 &gt; 集合通信测试”，设置任务信息，单击“确定”
+单机“创建”，输入“任务名称”及“任务描述” 单击任务名称，进入“任务配置”界面，导入节点信息进行连通性检测，完成后单击“下一步” 进入“分组配置”界面，单击“分组配置”在“自动分组”下输入“分组切片大小”为16，完成后单击“下一步”
+进入"参数配置"界面，在“测试参数配置”处设置相关参数，（测试数据起始大小1G，结束大小16G，遍历测试所有集合通信算子），完成后单击“下一步”
+进入“环境准备”界面，每次执行建议先进行“环境恢复”，再进行“环境检查”，完成后单击“下一步”
+进入“通信测试”界面，单击“执行”开始通信测试任务
+测试任务执行完成后，单击“导出测试报告”，保存测试结果</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -3180,7 +3142,11 @@
         </is>
       </c>
       <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>性能值单位换算方法：1TB/s=1024GB/s，1GB/s=1024MB/s，1MB/s=1024KB/s，1KB/s=1024B/s，1B/s=8bit/s</t>
+        </is>
+      </c>
       <c r="N41" t="n">
         <v>1</v>
       </c>
@@ -3213,7 +3179,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>集合通信性能测试-单Pod-32节点</t>
+          <t>基于Atlas 900 A3 SuperPoD服务器，使用CloudOps验收集群功能测试，进行参数面集合通信性能测试功能验收</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -3233,15 +3199,13 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>从工具CloudOps ToolKit首页菜单进入“AI训练 &gt; 服务器”页面。
-在AI训练-服务器界面右侧进入 “集群测试 &gt; 集合通信测试”，设置任务信息，单击“确定”。
-单机“创建”，输入“任务名称”及“任务描述”
-单击任务名称，进入“任务配置”界面，导入节点信息进行连通性检测，完成后单击“下一步”
-进入“分组配置”界面，单击“分组配置”在“自动分组”下输入“分组切片大小”为32，完成后单击“下一步”。
-进入"参数配置"界面，在“测试参数配置”处设置相关参数，（测试数据起始大小1G，结束大小16G，遍历测试所有集合通信算子），完成后单击“下一步”。
-进入“环境准备”界面，每次执行建议先进行“环境恢复”，再进行“环境检查”，完成后单击“下一步”。
-进入“通信测试”界面，单击“执行”开始通信测试任务。
-测试任务执行完成后，单击“导出测试报告”，保存测试结果。</t>
+          <t>从工具CloudOps ToolKit首页菜单进入“AI训练 &gt; 服务器”页面
+在AI训练-服务器界面右侧进入 “集群测试 &gt; 集合通信测试”，设置任务信息，单击“确定”
+单机“创建”，输入“任务名称”及“任务描述” 单击任务名称，进入“任务配置”界面，导入节点信息进行连通性检测，完成后单击“下一步” 进入“分组配置”界面，单击“分组配置”在“自动分组”下输入“分组切片大小”为32，完成后单击“下一步”
+进入"参数配置"界面，在“测试参数配置”处设置相关参数，（测试数据起始大小1G，结束大小16G，遍历测试所有集合通信算子），完成后单击“下一步”
+进入“环境准备”界面，每次执行建议先进行“环境恢复”，再进行“环境检查”，完成后单击“下一步”
+进入“通信测试”界面，单击“执行”开始通信测试任务
+测试任务执行完成后，单击“导出测试报告”，保存测试结果</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -3250,7 +3214,11 @@
         </is>
       </c>
       <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>性能值单位换算方法：1TB/s=1024GB/s，1GB/s=1024MB/s，1MB/s=1024KB/s，1KB/s=1024B/s，1B/s=8bit/s</t>
+        </is>
+      </c>
       <c r="N42" t="n">
         <v>1</v>
       </c>
@@ -3283,7 +3251,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>集合通信性能测试-单Pod-48节点</t>
+          <t>基于Atlas 900 A3 SuperPoD服务器，使用CloudOps验收集群功能测试，进行参数面集合通信性能测试功能验收</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -3303,15 +3271,13 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>从工具CloudOps ToolKit首页菜单进入“AI训练 &gt; 服务器”页面。
-在AI训练-服务器界面右侧进入 “集群测试 &gt; 集合通信测试”，设置任务信息，单击“确定”。
-单机“创建”，输入“任务名称”及“任务描述”
-单击任务名称，进入“任务配置”界面，导入节点信息进行连通性检测，完成后单击“下一步”
-进入“分组配置”界面，单击“分组配置”在“自动分组”下输入“分组切片大小”为48，完成后单击“下一步”。
-进入"参数配置"界面，在“测试参数配置”处设置相关参数，（测试数据起始大小1G，结束大小16G，遍历测试所有集合通信算子），完成后单击“下一步”。
-进入“环境准备”界面，每次执行建议先进行“环境恢复”，再进行“环境检查”，完成后单击“下一步”。
-进入“通信测试”界面，单击“执行”开始通信测试任务。
-测试任务执行完成后，单击“导出测试报告”，保存测试结果。</t>
+          <t>从工具CloudOps ToolKit首页菜单进入“AI训练 &gt; 服务器”页面
+在AI训练-服务器界面右侧进入 “集群测试 &gt; 集合通信测试”，设置任务信息，单击“确定”
+单机“创建”，输入“任务名称”及“任务描述” 单击任务名称，进入“任务配置”界面，导入节点信息进行连通性检测，完成后单击“下一步” 进入“分组配置”界面，单击“分组配置”在“自动分组”下输入“分组切片大小”为48，完成后单击“下一步”
+进入"参数配置"界面，在“测试参数配置”处设置相关参数，（测试数据起始大小1G，结束大小16G，遍历测试所有集合通信算子），完成后单击“下一步”
+进入“环境准备”界面，每次执行建议先进行“环境恢复”，再进行“环境检查”，完成后单击“下一步”
+进入“通信测试”界面，单击“执行”开始通信测试任务
+测试任务执行完成后，单击“导出测试报告”，保存测试结果</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -3320,7 +3286,11 @@
         </is>
       </c>
       <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>性能值单位换算方法：1TB/s=1024GB/s，1GB/s=1024MB/s，1MB/s=1024KB/s，1KB/s=1024B/s，1B/s=8bit/s</t>
+        </is>
+      </c>
       <c r="N43" t="n">
         <v>1</v>
       </c>
@@ -3353,7 +3323,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>集群集合通信测试-多Pod-16节点（2*8）</t>
+          <t>基于Atlas 900 A3 SuperPoD服务器，使用CloudOps验收集群功能测试，进行参数面集合通信性能测试功能验收</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -3373,15 +3343,13 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>从工具CloudOps ToolKit首页菜单进入“AI训练 &gt; 服务器”页面。
-在AI训练-服务器界面右侧进入 “集群测试 &gt; 集合通信测试”，设置任务信息，单击“确定”。
-单机“创建”，输入“任务名称”及“任务描述”
-单击任务名称，进入“任务配置”界面，从两个384超节点中各选取8台计算节点，导入节点信息进行连通性检测，完成后单击“下一步”
-进入“分组配置”界面，单击“分组配置”在“自动分组”下输入“分组切片大小”为16，完成后单击“下一步”。
-进入"参数配置"界面，在“测试参数配置”处设置相关参数，（测试数据起始大小1G，结束大小16G，遍历测试所有集合通信算子），完成后单击“下一步”。
-进入“环境准备”界面，每次执行建议先进行“环境恢复”，再进行“环境检查”，完成后单击“下一步”。
-进入“通信测试”界面，单击“执行”开始通信测试任务。
-测试任务执行完成后，单击“导出测试报告”，保存测试结果。</t>
+          <t>从工具CloudOps ToolKit首页菜单进入“AI训练 &gt; 服务器”页面
+在AI训练-服务器界面右侧进入 “集群测试 &gt; 集合通信测试”，设置任务信息，单击“确定”
+单机“创建”，输入“任务名称”及“任务描述” 单击任务名称，进入“任务配置”界面，从两个384超节点中各选取8台计算节点，导入节点信息进行连通性检测，完成后单击“下一步” 进入“分组配置”界面，单击“分组配置”在“自动分组”下输入“分组切片大小”为16，完成后单击“下一步”
+进入"参数配置"界面，在“测试参数配置”处设置相关参数，（测试数据起始大小1G，结束大小16G，遍历测试所有集合通信算子），完成后单击“下一步”
+进入“环境准备”界面，每次执行建议先进行“环境恢复”，再进行“环境检查”，完成后单击“下一步”
+进入“通信测试”界面，单击“执行”开始通信测试任务
+测试任务执行完成后，单击“导出测试报告”，保存测试结果</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -3390,7 +3358,11 @@
         </is>
       </c>
       <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>性能值单位换算方法：1TB/s=1024GB/s，1GB/s=1024MB/s，1MB/s=1024KB/s，1KB/s=1024B/s，1B/s=8bit/s</t>
+        </is>
+      </c>
       <c r="N44" t="n">
         <v>1</v>
       </c>
@@ -3423,7 +3395,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>集群集合通信测试-多Pod-24节点（3*8）</t>
+          <t>基于Atlas 900 A3 SuperPoD服务器，使用CloudOps验收集群功能测试，进行参数面集合通信性能测试功能验收</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -3443,15 +3415,13 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>从工具CloudOps ToolKit首页菜单进入“AI训练 &gt; 服务器”页面。
-在AI训练-服务器界面右侧进入 “集群测试 &gt; 集合通信测试”，设置任务信息，单击“确定”。
-单机“创建”，输入“任务名称”及“任务描述”
-单击任务名称，进入“任务配置”界面，从三个384超节点中各选取8台计算节点，导入节点信息进行连通性检测，完成后单击“下一步”
-进入“分组配置”界面，单击“分组配置”在“自动分组”下输入“分组切片大小”为24，完成后单击“下一步”。
-进入"参数配置"界面，在“测试参数配置”处设置相关参数，（测试数据起始大小1G，结束大小16G，遍历测试所有集合通信算子），完成后单击“下一步”。
-进入“环境准备”界面，每次执行建议先进行“环境恢复”，再进行“环境检查”，完成后单击“下一步”。
-进入“通信测试”界面，单击“执行”开始通信测试任务。
-测试任务执行完成后，单击“导出测试报告”，保存测试结果。</t>
+          <t>从工具CloudOps ToolKit首页菜单进入“AI训练 &gt; 服务器”页面
+在AI训练-服务器界面右侧进入 “集群测试 &gt; 集合通信测试”，设置任务信息，单击“确定”
+单机“创建”，输入“任务名称”及“任务描述” 单击任务名称，进入“任务配置”界面，从三个384超节点中各选取8台计算节点，导入节点信息进行连通性检测，完成后单击“下一步” 进入“分组配置”界面，单击“分组配置”在“自动分组”下输入“分组切片大小”为24，完成后单击“下一步”
+进入"参数配置"界面，在“测试参数配置”处设置相关参数，（测试数据起始大小1G，结束大小16G，遍历测试所有集合通信算子），完成后单击“下一步”
+进入“环境准备”界面，每次执行建议先进行“环境恢复”，再进行“环境检查”，完成后单击“下一步”
+进入“通信测试”界面，单击“执行”开始通信测试任务
+测试任务执行完成后，单击“导出测试报告”，保存测试结果</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -3460,7 +3430,11 @@
         </is>
       </c>
       <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>性能值单位换算方法：1TB/s=1024GB/s，1GB/s=1024MB/s，1MB/s=1024KB/s，1KB/s=1024B/s，1B/s=8bit/s</t>
+        </is>
+      </c>
       <c r="N45" t="n">
         <v>1</v>
       </c>
@@ -3493,7 +3467,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>集群集合通信测试-多Pod-32节点（4*8）</t>
+          <t>基于Atlas 900 A3 SuperPoD服务器，使用CloudOps验收集群功能测试，进行参数面集合通信性能测试功能验收</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -3513,15 +3487,13 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>从工具CloudOps ToolKit首页菜单进入“AI训练 &gt; 服务器”页面。
-在AI训练-服务器界面右侧进入 “集群测试 &gt; 集合通信测试”，设置任务信息，单击“确定”。
-单机“创建”，输入“任务名称”及“任务描述”
-单击任务名称，进入“任务配置”界面，从四个384超节点中各选取8台计算节点，导入节点信息进行连通性检测，完成后单击“下一步”
-进入“分组配置”界面，单击“分组配置”在“自动分组”下输入“分组切片大小”为32，完成后单击“下一步”。
-进入"参数配置"界面，在“测试参数配置”处设置相关参数，（测试数据起始大小1G，结束大小16G，遍历测试所有集合通信算子），完成后单击“下一步”。
-进入“环境准备”界面，每次执行建议先进行“环境恢复”，再进行“环境检查”，完成后单击“下一步”。
-进入“通信测试”界面，单击“执行”开始通信测试任务。
-测试任务执行完成后，单击“导出测试报告”，保存测试结果。</t>
+          <t>从工具CloudOps ToolKit首页菜单进入“AI训练 &gt; 服务器”页面
+在AI训练-服务器界面右侧进入 “集群测试 &gt; 集合通信测试”，设置任务信息，单击“确定”
+单机“创建”，输入“任务名称”及“任务描述” 单击任务名称，进入“任务配置”界面，从四个384超节点中各选取8台计算节点，导入节点信息进行连通性检测，完成后单击“下一步” 进入“分组配置”界面，单击“分组配置”在“自动分组”下输入“分组切片大小”为32，完成后单击“下一步”
+进入"参数配置"界面，在“测试参数配置”处设置相关参数，（测试数据起始大小1G，结束大小16G，遍历测试所有集合通信算子），完成后单击“下一步”
+进入“环境准备”界面，每次执行建议先进行“环境恢复”，再进行“环境检查”，完成后单击“下一步”
+进入“通信测试”界面，单击“执行”开始通信测试任务
+测试任务执行完成后，单击“导出测试报告”，保存测试结果</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -3530,7 +3502,11 @@
         </is>
       </c>
       <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>性能值单位换算方法：1TB/s=1024GB/s，1GB/s=1024MB/s，1MB/s=1024KB/s，1KB/s=1024B/s，1B/s=8bit/s</t>
+        </is>
+      </c>
       <c r="N46" t="n">
         <v>1</v>
       </c>
@@ -3563,7 +3539,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>集群集合通信测试-多Pod-48节点（6*8）</t>
+          <t>基于Atlas 900 A3 SuperPoD服务器，使用CloudOps验收集群功能测试，进行参数面集合通信性能测试功能验收</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -3583,15 +3559,13 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>从工具CloudOps ToolKit首页菜单进入“AI训练 &gt; 服务器”页面。
-在AI训练-服务器界面右侧进入 “集群测试 &gt; 集合通信测试”，设置任务信息，单击“确定”。
-单机“创建”，输入“任务名称”及“任务描述”
-单击任务名称，进入“任务配置”界面，从六个384超节点中各选取8台计算节点，导入节点信息进行连通性检测，完成后单击“下一步”
-进入“分组配置”界面，单击“分组配置”在“自动分组”下输入“分组切片大小”为48，完成后单击“下一步”。
-进入"参数配置"界面，在“测试参数配置”处设置相关参数，（测试数据起始大小1G，结束大小16G，遍历测试所有集合通信算子），完成后单击“下一步”。
-进入“环境准备”界面，每次执行建议先进行“环境恢复”，再进行“环境检查”，完成后单击“下一步”。
-进入“通信测试”界面，单击“执行”开始通信测试任务。
-测试任务执行完成后，单击“导出测试报告”，保存测试结果。</t>
+          <t>从工具CloudOps ToolKit首页菜单进入“AI训练 &gt; 服务器”页面
+在AI训练-服务器界面右侧进入 “集群测试 &gt; 集合通信测试”，设置任务信息，单击“确定”
+单机“创建”，输入“任务名称”及“任务描述” 单击任务名称，进入“任务配置”界面，从六个384超节点中各选取8台计算节点，导入节点信息进行连通性检测，完成后单击“下一步” 进入“分组配置”界面，单击“分组配置”在“自动分组”下输入“分组切片大小”为48，完成后单击“下一步”
+进入"参数配置"界面，在“测试参数配置”处设置相关参数，（测试数据起始大小1G，结束大小16G，遍历测试所有集合通信算子），完成后单击“下一步”
+进入“环境准备”界面，每次执行建议先进行“环境恢复”，再进行“环境检查”，完成后单击“下一步”
+进入“通信测试”界面，单击“执行”开始通信测试任务
+测试任务执行完成后，单击“导出测试报告”，保存测试结果</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -3600,7 +3574,11 @@
         </is>
       </c>
       <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>性能值单位换算方法：1TB/s=1024GB/s，1GB/s=1024MB/s，1MB/s=1024KB/s，1KB/s=1024B/s，1B/s=8bit/s</t>
+        </is>
+      </c>
       <c r="N47" t="n">
         <v>1</v>
       </c>
@@ -3618,7 +3596,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>3.4.1</t>
+          <t>3.3.5</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -3628,22 +3606,22 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>模型集群训练性能测试-单Pod</t>
+          <t>集群集合通信测试-多Pod</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>qwen3-32B训练测试-单Pod-4节点</t>
+          <t>基于Atlas 900 A3 SuperPoD服务器，使用CloudOps验收集群功能测试，进行参数面集合通信性能测试功能验收</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>基于Atlas 900 A3 SuperPoD服务器，进行典型稠密模型训练摸高</t>
+          <t>基于Atlas 900 A3 SuperPoD服务器，使用CloudOps验收集群功能测试，进行参数面集合通信性能测试功能验收</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>单个384超节点</t>
+          <t>两个384超节点</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -3653,27 +3631,26 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>在CloudOps工具首页选择“服务器 &gt; 开局交付 &gt; 集群测试”，进入“集群测试”页面。
-单击“集群测试”
-单击“集群训练测试”，进入集群训练测试界面。
-节点选择中，选择同一超节点内的4台计算节点
-模型类型选择qwen3-32B
-在训练参数配置中点击“引用模板配置”，选择“qwen3_32b_4节点_A3参数配置模板”
-单击“下一步”，进入“环境检查”界面
-上传模型镜像文件。若待训练的节点服务器已包含模型镜像文件，可直接单击“下一步”，跳过本步骤
-进入“测试执行”界面，启动测试
-集群训练过程中，可单击“查询最新状态”查看训练状态。服务器启动训练任务后，可单击“查询日志”，选择集群的尾节点IP（步骤4.2.a模板中配置的集群的最后一台节点），单击“刷新”，查看工具运行日志和训练日志。
-测试完成后（“当前状态”显示训练任务已完成），可单击“生成报告”，将测试报告保存至本地</t>
+          <t>从工具CloudOps ToolKit首页菜单进入“AI训练 &gt; 服务器”页面
+在AI训练-服务器界面右侧进入 “集群测试 &gt; 集合通信测试”，设置任务信息，单击“确定”
+单机“创建”，输入“任务名称”及“任务描述” 单击任务名称，进入“任务配置”界面，从两个384超节点中各选取48台计算节点，导入节点信息进行连通性检测，完成后单击“下一步” 进入“分组配置”界面，单击“分组配置”在“自动分组”下输入“分组切片大小”为96，完成后单击“下一步”
+进入"参数配置"界面，在“测试参数配置”处设置相关参数，（测试数据起始大小1G，结束大小16G，遍历测试所有集合通信算子），完成后单击“下一步”
+进入“环境准备”界面，每次执行建议先进行“环境恢复”，再进行“环境检查”，完成后单击“下一步”
+进入“通信测试”界面，单击“执行”开始通信测试任务
+测试任务执行完成后，单击“导出测试报告”，保存测试结果</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>收集并分析训练日志，模型正常训练，测试结果为“ PASS”。
-4节点单步平均耗时不超过76500 ms；</t>
+          <t>2*满配超节点在1G数据量下，allreduce带宽不低于89GB/s</t>
         </is>
       </c>
       <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>性能值单位换算方法：1TB/s=1024GB/s，1GB/s=1024MB/s，1MB/s=1024KB/s，1KB/s=1024B/s，1B/s=8bit/s</t>
+        </is>
+      </c>
       <c r="N48" t="n">
         <v>1</v>
       </c>
@@ -3691,7 +3668,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>3.4.2</t>
+          <t>3.3.6</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -3701,22 +3678,22 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>模型集群训练性能测试-单Pod</t>
+          <t>集群集合通信测试-多Pod</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>qwen3-32B训练测试-单Pod-8节点</t>
+          <t>基于Atlas 900 A3 SuperPoD服务器，使用CloudOps验收集群功能测试，进行参数面集合通信性能测试功能验收</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>基于Atlas 900 A3 SuperPoD服务器，进行典型稠密模型训练摸高</t>
+          <t>基于Atlas 900 A3 SuperPoD服务器，使用CloudOps验收集群功能测试，进行参数面集合通信性能测试功能验收</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>单个384超节点</t>
+          <t>四个384超节点</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3726,27 +3703,26 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>在CloudOps工具首页选择“服务器 &gt; 开局交付 &gt; 集群测试”，进入“集群测试”页面。
-单击“集群测试”
-单击“集群训练测试”，进入集群训练测试界面。
-节点选择中，选择同一超节点内的8台计算节点
-模型类型选择qwen3-32B
-在训练参数配置中点击“引用模板配置”，选择“qwen3_32b_8节点_A3参数配置模板”
-单击“下一步”，进入“环境检查”界面
-上传模型镜像文件。若待训练的节点服务器已包含模型镜像文件，可直接单击“下一步”，跳过本步骤
-进入“测试执行”界面，启动测试
-集群训练过程中，可单击“查询最新状态”查看训练状态。服务器启动训练任务后，可单击“查询日志”，选择集群的尾节点IP（步骤4.2.a模板中配置的集群的最后一台节点），单击“刷新”，查看工具运行日志和训练日志。
-测试完成后（“当前状态”显示训练任务已完成），可单击“生成报告”，将测试报告保存至本地</t>
+          <t>从工具CloudOps ToolKit首页菜单进入“AI训练 &gt; 服务器”页面
+在AI训练-服务器界面右侧进入 “集群测试 &gt; 集合通信测试”，设置任务信息，单击“确定”
+单机“创建”，输入“任务名称”及“任务描述” 单击任务名称，进入“任务配置”界面，从四个384超节点中各选取48台计算节点，导入节点信息进行连通性检测，完成后单击“下一步” 进入“分组配置”界面，单击“分组配置”在“自动分组”下输入“分组切片大小”为192，完成后单击“下一步”
+进入"参数配置"界面，在“测试参数配置”处设置相关参数，（测试数据起始大小1G，结束大小16G，遍历测试所有集合通信算子），完成后单击“下一步”
+进入“环境准备”界面，每次执行建议先进行“环境恢复”，再进行“环境检查”，完成后单击“下一步”
+进入“通信测试”界面，单击“执行”开始通信测试任务
+测试任务执行完成后，单击“导出测试报告”，保存测试结果</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>收集并分析训练日志，模型正常训练，测试结果为“ PASS”。
-8节点单步平均耗时不超过76500 ms；</t>
+          <t>4*满配超节点在1G数据量下，allreduce带宽不低于89GB/s</t>
         </is>
       </c>
       <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>性能值单位换算方法：1TB/s=1024GB/s，1GB/s=1024MB/s，1MB/s=1024KB/s，1KB/s=1024B/s，1B/s=8bit/s</t>
+        </is>
+      </c>
       <c r="N49" t="n">
         <v>1</v>
       </c>
@@ -3764,7 +3740,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>3.4.3</t>
+          <t>3.4.1</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -3779,7 +3755,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>qwen3-32B训练测试-单Pod-16节点</t>
+          <t>基于Atlas 900 A3 SuperPoD服务器，进行典型稠密模型训练摸高</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -3799,23 +3775,16 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>在CloudOps工具首页选择“服务器 &gt; 开局交付 &gt; 集群测试”，进入“集群测试”页面。
-单击“集群测试”
-单击“集群训练测试”，进入集群训练测试界面。
-节点选择中，选择同一超节点内的16台计算节点
-模型类型选择qwen3-32B
-在训练参数配置中点击“引用模板配置”，选择“qwen3_32b_16节点_A3参数配置模板”
-单击“下一步”，进入“环境检查”界面
-上传模型镜像文件。若待训练的节点服务器已包含模型镜像文件，可直接单击“下一步”，跳过本步骤
-进入“测试执行”界面，启动测试
-集群训练过程中，可单击“查询最新状态”查看训练状态。服务器启动训练任务后，可单击“查询日志”，选择集群的尾节点IP（步骤4.2.a模板中配置的集群的最后一台节点），单击“刷新”，查看工具运行日志和训练日志。
+          <t>在CloudOps工具首页选择“服务器 &gt; 开局交付 &gt; 集群测试”，进入“集群测试”页面
+单击“集群测试” 单击“集群训练测试”，进入集群训练测试界面
+节点选择中，选择同一超节点内的4台计算节点 模型类型选择qwen3-32B 在训练参数配置中点击“引用模板配置”，选择“qwen3_32b_4节点_A3参数配置模板”  单击“下一步”，进入“环境检查”界面 上传模型镜像文件。若待训练的节点服务器已包含模型镜像文件，可直接单击“下一步”，跳过本步骤 进入“测试执行”界面，启动测试 集群训练过程中，可单击“查询最新状态”查看训练状态。服务器启动训练任务后，可单击“查询日志”，选择集群的尾节点IP（步骤4.2.a模板中配置的集群的最后一台节点），单击“刷新”，查看工具运行日志和训练日志
 测试完成后（“当前状态”显示训练任务已完成），可单击“生成报告”，将测试报告保存至本地</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>收集并分析训练日志，模型正常训练，测试结果为“ PASS”。
-16节点单步平均耗时不超过78500 ms。</t>
+          <t>收集并分析训练日志，模型正常训练，测试结果为“ PASS”
+4节点单步平均耗时不超过76500 ms；</t>
         </is>
       </c>
       <c r="L50" t="inlineStr"/>
@@ -3837,7 +3806,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>3.4.3</t>
+          <t>3.4.2</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -3852,7 +3821,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>qwen3-32B训练测试-单Pod-16节点</t>
+          <t>基于Atlas 900 A3 SuperPoD服务器，进行典型稠密模型训练摸高</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -3872,23 +3841,16 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>在CloudOps工具首页选择“服务器 &gt; 开局交付 &gt; 集群测试”，进入“集群测试”页面。
-单击“集群测试”
-单击“集群训练测试”，进入集群训练测试界面。
-节点选择中，选择同一超节点内的32台计算节点
-模型类型选择qwen3-32B
-在训练参数配置中点击“引用模板配置”，选择“qwen3_32b_32节点_A3参数配置模板”
-单击“下一步”，进入“环境检查”界面
-上传模型镜像文件。若待训练的节点服务器已包含模型镜像文件，可直接单击“下一步”，跳过本步骤
-进入“测试执行”界面，启动测试
-集群训练过程中，可单击“查询最新状态”查看训练状态。服务器启动训练任务后，可单击“查询日志”，选择集群的尾节点IP（步骤4.2.a模板中配置的集群的最后一台节点），单击“刷新”，查看工具运行日志和训练日志。
+          <t>在CloudOps工具首页选择“服务器 &gt; 开局交付 &gt; 集群测试”，进入“集群测试”页面
+单击“集群测试” 单击“集群训练测试”，进入集群训练测试界面
+节点选择中，选择同一超节点内的8台计算节点 模型类型选择qwen3-32B 在训练参数配置中点击“引用模板配置”，选择“qwen3_32b_8节点_A3参数配置模板” 单击“下一步”，进入“环境检查”界面 上传模型镜像文件。若待训练的节点服务器已包含模型镜像文件，可直接单击“下一步”，跳过本步骤 进入“测试执行”界面，启动测试 集群训练过程中，可单击“查询最新状态”查看训练状态。服务器启动训练任务后，可单击“查询日志”，选择集群的尾节点IP（步骤4.2.a模板中配置的集群的最后一台节点），单击“刷新”，查看工具运行日志和训练日志
 测试完成后（“当前状态”显示训练任务已完成），可单击“生成报告”，将测试报告保存至本地</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>收集并分析训练日志，模型正常训练，测试结果为“ PASS”。
-32节点单步平均耗时不超过78500 ms。</t>
+          <t>收集并分析训练日志，模型正常训练，测试结果为“ PASS”
+8节点单步平均耗时不超过76500 ms；</t>
         </is>
       </c>
       <c r="L51" t="inlineStr"/>
@@ -3910,7 +3872,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>3.4.4</t>
+          <t>3.4.3</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -3925,7 +3887,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>qwen3-32B训练测试-单Pod-32节点</t>
+          <t>基于Atlas 900 A3 SuperPoD服务器，进行典型稠密模型训练摸高</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -3945,23 +3907,16 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>在CloudOps工具首页选择“服务器 &gt; 开局交付 &gt; 集群测试”，进入“集群测试”页面。
-单击“集群测试”
-单击“集群训练测试”，进入集群训练测试界面。
-节点选择中，选择同一超节点内的48台计算节点
-模型类型选择qwen3-32B
-在训练参数配置中点击“引用模板配置”，选择“qwen3_32b_48节点_A3参数配置模板”
-单击“下一步”，进入“环境检查”界面
-上传模型镜像文件。若待训练的节点服务器已包含模型镜像文件，可直接单击“下一步”，跳过本步骤
-进入“测试执行”界面，启动测试
-集群训练过程中，可单击“查询最新状态”查看训练状态。服务器启动训练任务后，可单击“查询日志”，选择集群的尾节点IP（步骤4.2.a模板中配置的集群的最后一台节点），单击“刷新”，查看工具运行日志和训练日志。
+          <t>在CloudOps工具首页选择“服务器 &gt; 开局交付 &gt; 集群测试”，进入“集群测试”页面
+单击“集群测试” 单击“集群训练测试”，进入集群训练测试界面
+节点选择中，选择同一超节点内的32台计算节点 模型类型选择qwen3-32B 在训练参数配置中点击“引用模板配置”，选择“qwen3_32b_32节点_A3参数配置模板” 单击“下一步”，进入“环境检查”界面 上传模型镜像文件。若待训练的节点服务器已包含模型镜像文件，可直接单击“下一步”，跳过本步骤 进入“测试执行”界面，启动测试 集群训练过程中，可单击“查询最新状态”查看训练状态。服务器启动训练任务后，可单击“查询日志”，选择集群的尾节点IP（步骤4.2.a模板中配置的集群的最后一台节点），单击“刷新”，查看工具运行日志和训练日志
 测试完成后（“当前状态”显示训练任务已完成），可单击“生成报告”，将测试报告保存至本地</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>收集并分析训练日志，模型正常训练，测试结果为“ PASS”。
-48节点单步平均耗时不超过78500 ms。</t>
+          <t>收集并分析训练日志，模型正常训练，测试结果为“ PASS”
+32节点单步平均耗时不超过78500 ms</t>
         </is>
       </c>
       <c r="L52" t="inlineStr"/>
@@ -3983,7 +3938,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>3.5.1</t>
+          <t>3.4.4</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -3993,22 +3948,22 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>集群训练稳定性测试</t>
+          <t>模型集群训练性能测试-单Pod</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Qwen3-32B模型训练稳定性测试</t>
+          <t>基于Atlas 900 A3 SuperPoD服务器，进行典型稠密模型训练摸高</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>基于Atlas 900 A3 SuperPoD服务器，进行模型稳定性测试</t>
+          <t>基于Atlas 900 A3 SuperPoD服务器，进行典型稠密模型训练摸高</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>384超节点</t>
+          <t>单个384超节点</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -4018,28 +3973,88 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>在CloudOps工具首页选择“服务器 &gt; 开局交付 &gt; 集群测试”，进入“集群测试”页面。
-单击“集群测试”
-单击“集群训练测试”，进入集群训练测试界面。
-模型选择qwen3-32B
-参数配置（参考算力军团发布的模型测试基线）
-注意：--train-iters 训练步数，设置为800步，训练 时长大约为12小时，满足训练 长稳要求；如果用户对训练长 稳时间有其他要求，可根据900 步每12小时来换算训练步数。
-单击“下一步”，进入“环境检查”界面
-上传模型镜像文件。若待训练的节点服务器已包含模型镜像文件，可直接单击“下一步”，跳过本步骤
-进入“测试执行”界面，启动测试
-集群训练过程中，可单击“查询最新状态”查看训练状态。服务器启动训练任务后，可单击“查询日志”，选择集群的尾节点IP（步骤4.2.a模板中配置的集群的最后一台节点），单击“刷新”，查看工具运行日志和训练日志。
+          <t>在CloudOps工具首页选择“服务器 &gt; 开局交付 &gt; 集群测试”，进入“集群测试”页面
+单击“集群测试” 单击“集群训练测试”，进入集群训练测试界面
+节点选择中，选择同一超节点内的48台计算节点 模型类型选择qwen3-32B 在训练参数配置中点击“引用模板配置”，选择“qwen3_32b_48节点_A3参数配置模板” 单击“下一步”，进入“环境检查”界面 上传模型镜像文件。若待训练的节点服务器已包含模型镜像文件，可直接单击“下一步”，跳过本步骤 进入“测试执行”界面，启动测试 集群训练过程中，可单击“查询最新状态”查看训练状态。服务器启动训练任务后，可单击“查询日志”，选择集群的尾节点IP（步骤4.2.a模板中配置的集群的最后一台节点），单击“刷新”，查看工具运行日志和训练日志
 测试完成后（“当前状态”显示训练任务已完成），可单击“生成报告”，将测试报告保存至本地</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>收集并分析训练日志，训练效果与军团发布的模型测试参数配置预期一致；
-模型单步训练性能波动范围不超过10%。</t>
+          <t>收集并分析训练日志，模型正常训练，测试结果为“ PASS”
+48节点单步平均耗时不超过78500 ms</t>
         </is>
       </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr"/>
       <c r="N53" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>京东三期</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>3.5.1</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>算力集群性能测试用例</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>集群训练稳定性测试</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>基于Atlas 900 A3 SuperPoD服务器，进行模型稳定性测试</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>基于Atlas 900 A3 SuperPoD服务器，进行模型稳定性测试</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>384超节点</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>已参照版本配套完成相关软件包与脚本准备。 CloudOps Toolkit已完成配置信息导入。 服务器OS已完成安装，root用户可远程访问。 工具与服务器管理网络联通。</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>在CloudOps工具首页选择“服务器 &gt; 开局交付 &gt; 集群测试”，进入“集群测试”页面
+单击“集群测试” 单击“集群训练测试”，进入集群训练测试界面
+模型选择qwen3-32B 参数配置（参考算力军团发布的模型测试基线） 注意：--train-iters 训练步数，设置为800步，训练 时长大约为12小时，满足训练 长稳要求；如果用户对训练长 稳时间有其他要求，可根据900 步每12小时来换算训练步数
+单击“下一步”，进入“环境检查”界面 上传模型镜像文件。若待训练的节点服务器已包含模型镜像文件，可直接单击“下一步”，跳过本步骤 进入“测试执行”界面，启动测试 集群训练过程中，可单击“查询最新状态”查看训练状态。服务器启动训练任务后，可单击“查询日志”，选择集群的尾节点IP（步骤4.2.a模板中配置的集群的最后一台节点），单击“刷新”，查看工具运行日志和训练日志
+测试完成后（“当前状态”显示训练任务已完成），可单击“生成报告”，将测试报告保存至本地</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>收集并分析训练日志，训练效果与军团发布的模型测试参数配置预期一致
+模型单步训练性能波动范围不超过10%</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="n">
         <v>1</v>
       </c>
     </row>
